--- a/SSA_agent/concept_db/sources.xlsx
+++ b/SSA_agent/concept_db/sources.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="130">
   <si>
     <t>source_id</t>
   </si>
@@ -22,6 +22,9 @@
     <t>title</t>
   </si>
   <si>
+    <t>link</t>
+  </si>
+  <si>
     <t>content</t>
   </si>
   <si>
@@ -164,6 +167,147 @@
   </si>
   <si>
     <t>Review of Autonomous Space Robotic Manipulators for On-Orbit Servicing and Active Debris Removal</t>
+  </si>
+  <si>
+    <t>https://www.universetoday.com/articles/scientists-publish-the-first-direct-measurement-of-space-debris-pollution</t>
+  </si>
+  <si>
+    <t>https://www.science.org/doi/10.1126/science.aee0657</t>
+  </si>
+  <si>
+    <t>https://www.sciencenews.org/article/rocket-reentry-metal-pollution-detected</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s44453-025-00014-9</t>
+  </si>
+  <si>
+    <t>https://spacenews.com/uncontrolled-experiment-study-links-harmful-atmospheric-metals-to-spacecraft-reentry/</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/astronomy-and-space-sciences/articles/10.3389/fspas.2025.1572313/full</t>
+  </si>
+  <si>
+    <t>https://builtin.com/articles/space-debris</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s44453-025-00007-8</t>
+  </si>
+  <si>
+    <t>https://aerospace.org/space-debris</t>
+  </si>
+  <si>
+    <t>https://www.weforum.org/stories/2023/06/orbital-debris-space-junk-removal/</t>
+  </si>
+  <si>
+    <t>https://www.frontiersin.org/journals/communications-and-networks/articles/10.3389/frcmn.2026.1730921/full</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s40494-026-02378-x</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s44459-025-00008-9</t>
+  </si>
+  <si>
+    <t>https://www.thehindu.com/sci-tech/science/satellites-science-and-the-new-fight-for-spectrum-in-space/article70380429.ece</t>
+  </si>
+  <si>
+    <t>https://spectrum.ieee.org/vera-rubin-observatory-first-images</t>
+  </si>
+  <si>
+    <t>https://www.cambridge.org/core/journals/european-law-open/article/europes-expanding-coordination-space/33735B2D16E13AAC0CA9EB0AEB37C287</t>
+  </si>
+  <si>
+    <t>https://ccianet.org/articles/icymi-the-future-of-satellite-spectrum/</t>
+  </si>
+  <si>
+    <t>https://broadbandbreakfast.com/fcc-space-bureau-chief-highlights-role-of-leo-satellites-in-broadband-expansion/</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41467-025-64219-y</t>
+  </si>
+  <si>
+    <t>https://www.wfw.com/articles/spectrum-rights-and-orbital-positions-what-do-space-operators-need-to-know/</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41598-025-15988-5</t>
+  </si>
+  <si>
+    <t>https://www.spacecom.mil/Newsroom/News/Article-Display/Article/4308024/press-release-us-and-uk-demonstrate-partnership-in-first-ever-on-orbit-operation/</t>
+  </si>
+  <si>
+    <t>https://spacenews.com/starfish-space-and-impulse-space-demonstrate-autonomous-spacecraft-proximity-operations/</t>
+  </si>
+  <si>
+    <t>https://www.northropgrumman.com/what-we-do/space/space-logistics-services/space-industrial-revolution</t>
+  </si>
+  <si>
+    <t>https://www.nasaspaceflight.com/2025/12/starfish-space-rpo-impulse-space/</t>
+  </si>
+  <si>
+    <t>https://www.lockheedmartin.com/en-us/news/features/2025/docking-orion.html</t>
+  </si>
+  <si>
+    <t>https://uasmagazine.com/articles/northrop-grumman-demonstrates-autonomous-rendezvous-and-docking-technology-with-starlab-commercial-space-station</t>
+  </si>
+  <si>
+    <t>https://arstechnica.com/space/2025/12/two-space-startups-prove-you-dont-need-to-break-the-bank-to-rendezvous-in-space/</t>
+  </si>
+  <si>
+    <t>https://spacenews.com/u-s-uk-space-commands-execute-first-joint-satellite-maneuvers/</t>
+  </si>
+  <si>
+    <t>https://www.executivebiz.com/articles/northrop-secures-ussf-contract-to-support-in-space-refueling-program</t>
+  </si>
+  <si>
+    <t>https://www.raf.mod.uk/news/articles/sky-is-no-longer-the-limit-for-uk-us-military-operations/</t>
+  </si>
+  <si>
+    <t>https://www.scmp.com/news/china/science/article/3316605/china-could-be-about-attempt-landmark-satellite-refuelling-test</t>
+  </si>
+  <si>
+    <t>https://www.airuniversity.af.edu/Wild-Blue-Yonder/Articles/Article-Display/Article/2538269/satellite-servicing-a-history-the-impact-to-the-space-force-and-the-logistics-b/</t>
+  </si>
+  <si>
+    <t>https://spacenews.com/what-problem-is-charging-for-space-situational-awareness-supposed-to-solve/</t>
+  </si>
+  <si>
+    <t>https://www.airuniversity.af.edu/CASI/Display/Article/4315534/chinas-commercial-ssa-company-and-tle-localization/</t>
+  </si>
+  <si>
+    <t>https://www.airandspaceforces.com/article/world-space-21/</t>
+  </si>
+  <si>
+    <t>https://www.executivegov.com/articles/osc-commercial-conjunction-assessment-screening-services-pilot</t>
+  </si>
+  <si>
+    <t>https://room.eu.com/article/space-sustainability-and-the-role-of-space-situational-awareness</t>
+  </si>
+  <si>
+    <t>https://spacenews.com/managing-space-domain-awareness-data-has-become-a-greater-challenge-than-collecting-it/</t>
+  </si>
+  <si>
+    <t>https://www.copernicus.eu/en/news/news/observer-space-situational-awareness-europes-eyes-space</t>
+  </si>
+  <si>
+    <t>https://www.moneycontrol.com/technology/india-drafts-space-traffic-safety-rules-as-orbital-congestion-and-ssa-market-grows-article-13753808.html</t>
+  </si>
+  <si>
+    <t>https://www.spacecom.mil/Newsroom/News/Article-Display/Article/3921174/us-space-command-begins-dual-track-operations-of-spaceflight-safety-services-wi/</t>
+  </si>
+  <si>
+    <t>https://www.slingshot.space/news/amos-recap-revolutionizing-space-situational-awareness-through-applied-ai-ml</t>
+  </si>
+  <si>
+    <t>https://www.findarticles.com/digantara-raises-50m-for-space-based-missile-defense/</t>
+  </si>
+  <si>
+    <t>https://www.propublica.org/article/faa-trump-space-junk-safety-spacex-rockets</t>
+  </si>
+  <si>
+    <t>https://www.space.com/spacex-starlink-satellites.html</t>
+  </si>
+  <si>
+    <t>https://spj.science.org/doi/10.34133/space.0291</t>
   </si>
   <si>
     <t>Back in February 2025, a SpaceX rocket that had delivered 22 Starlink satellites to orbit had a malfunction. It failed to execute a planned deorbit burn and drifted for 18 days in orbit before beginning an uncontrolled descent about 100km off the west coast of Ireland. Some parts of the rocket landed in Poland, and while they didn’t injure anybody, there was enough concern about the lack of communication that Poland dismissed the head of its space agency. But that wasn't the only lasting impact of this failure. A new paper from Robin Wing and her colleagues at the Leibniz Institute for Atmospheric Physics, published in Communications Earth &amp; Environment ties that specific rocket reentry to a massive plume of pollution for the first time.
@@ -1422,7 +1566,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1437,6 +1581,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1471,16 +1622,22 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1773,10 +1930,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1786,480 +1943,673 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>6</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>7</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>8</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="D6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>9</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>11</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>14</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>15</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+        <v>17</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>18</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D16" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
+        <v>19</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>19</v>
-      </c>
-      <c r="C18" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+        <v>20</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
+        <v>21</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
+        <v>22</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
+        <v>23</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
+        <v>24</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
+        <v>25</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
-      </c>
-      <c r="C24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
+        <v>26</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
       <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
-      </c>
-      <c r="C25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+        <v>27</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D25" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
       <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>28</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4">
       <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>29</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D27" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4">
       <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>29</v>
-      </c>
-      <c r="C28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
+        <v>30</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D28" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4">
       <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>30</v>
-      </c>
-      <c r="C29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>31</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4">
       <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
+        <v>32</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4">
       <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>32</v>
-      </c>
-      <c r="C31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
+        <v>33</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4">
       <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
+        <v>34</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
       <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
+        <v>35</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
       <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
+        <v>36</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
       <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C35" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
+        <v>37</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
       <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
+        <v>38</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
+        <v>39</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D37" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
       <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C38" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+        <v>40</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
       <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
-      </c>
-      <c r="C39" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
+        <v>41</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D39" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
       <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
+        <v>42</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
       <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
+        <v>43</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
       <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
+        <v>44</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4">
       <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
+        <v>45</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4">
       <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
-      </c>
-      <c r="C44" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
+        <v>46</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
       <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
-      </c>
-      <c r="C45" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
+        <v>47</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D45" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4">
       <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
-      </c>
-      <c r="C46" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
+        <v>48</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4">
       <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>48</v>
-      </c>
-      <c r="C47" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+        <v>49</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4">
       <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C2" r:id="rId1"/>
+    <hyperlink ref="C3" r:id="rId2"/>
+    <hyperlink ref="C4" r:id="rId3"/>
+    <hyperlink ref="C5" r:id="rId4"/>
+    <hyperlink ref="C6" r:id="rId5"/>
+    <hyperlink ref="C7" r:id="rId6"/>
+    <hyperlink ref="C8" r:id="rId7"/>
+    <hyperlink ref="C9" r:id="rId8"/>
+    <hyperlink ref="C10" r:id="rId9"/>
+    <hyperlink ref="C11" r:id="rId10"/>
+    <hyperlink ref="C12" r:id="rId11"/>
+    <hyperlink ref="C13" r:id="rId12"/>
+    <hyperlink ref="C14" r:id="rId13"/>
+    <hyperlink ref="C15" r:id="rId14"/>
+    <hyperlink ref="C16" r:id="rId15"/>
+    <hyperlink ref="C17" r:id="rId16"/>
+    <hyperlink ref="C18" r:id="rId17"/>
+    <hyperlink ref="C19" r:id="rId18"/>
+    <hyperlink ref="C20" r:id="rId19"/>
+    <hyperlink ref="C21" r:id="rId20"/>
+    <hyperlink ref="C22" r:id="rId21"/>
+    <hyperlink ref="C23" r:id="rId22"/>
+    <hyperlink ref="C24" r:id="rId23"/>
+    <hyperlink ref="C25" r:id="rId24"/>
+    <hyperlink ref="C26" r:id="rId25"/>
+    <hyperlink ref="C27" r:id="rId26"/>
+    <hyperlink ref="C28" r:id="rId27"/>
+    <hyperlink ref="C29" r:id="rId28"/>
+    <hyperlink ref="C30" r:id="rId29"/>
+    <hyperlink ref="C31" r:id="rId30"/>
+    <hyperlink ref="C32" r:id="rId31"/>
+    <hyperlink ref="C33" r:id="rId32"/>
+    <hyperlink ref="C34" r:id="rId33"/>
+    <hyperlink ref="C35" r:id="rId34"/>
+    <hyperlink ref="C36" r:id="rId35"/>
+    <hyperlink ref="C37" r:id="rId36"/>
+    <hyperlink ref="C38" r:id="rId37"/>
+    <hyperlink ref="C39" r:id="rId38"/>
+    <hyperlink ref="C40" r:id="rId39"/>
+    <hyperlink ref="C41" r:id="rId40"/>
+    <hyperlink ref="C42" r:id="rId41"/>
+    <hyperlink ref="C43" r:id="rId42"/>
+    <hyperlink ref="C44" r:id="rId43"/>
+    <hyperlink ref="C45" r:id="rId44"/>
+    <hyperlink ref="C46" r:id="rId45"/>
+    <hyperlink ref="C47" r:id="rId46"/>
+    <hyperlink ref="C48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>